--- a/isles24_summary.xlsx
+++ b/isles24_summary.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>M: 132 (54.3%), F: 111 (45.7%)</t>
+          <t>M: 132 (53.2%), F: 111 (44.8%), Unknown: 5 (2.0%)</t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>0: 174 (71.6%), 1: 69 (28.4%)</t>
+          <t>0: 174 (70.2%), 1: 69 (27.8%), Unknown: 5 (2.0%)</t>
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>1: 151 (61.9%), 0: 93 (38.1%)</t>
+          <t>1: 151 (60.9%), 0: 93 (37.5%), Unknown: 4 (1.6%)</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>0: 203 (83.9%), 1: 39 (16.1%)</t>
+          <t>0: 203 (81.9%), 1: 39 (15.7%), Unknown: 6 (2.4%)</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>0: 151 (62.7%), 1: 90 (37.3%)</t>
+          <t>0: 151 (60.9%), 1: 90 (36.3%), Unknown: 7 (2.8%)</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>0: 198 (82.8%), 1: 41 (17.2%)</t>
+          <t>0: 198 (79.8%), 1: 41 (16.5%), Unknown: 9 (3.6%)</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>0: 157 (65.7%), 1: 82 (34.3%)</t>
+          <t>0: 157 (63.3%), 1: 82 (33.1%), Unknown: 9 (3.6%)</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>0: 180 (75.0%), 1: 60 (25.0%)</t>
+          <t>0: 180 (72.6%), 1: 60 (24.2%), Unknown: 8 (3.2%)</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>0: 177 (73.1%), 1: 65 (26.9%)</t>
+          <t>0: 177 (71.4%), 1: 65 (26.2%), Unknown: 6 (2.4%)</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>0: 212 (96.4%), 1: 8 (3.6%)</t>
+          <t>0: 212 (85.5%), 1: 8 (3.2%), Unknown: 28 (11.3%)</t>
         </is>
       </c>
       <c r="Q17" s="4" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>0: 215 (88.1%), 1: 29 (11.9%)</t>
+          <t>0: 215 (86.7%), 1: 29 (11.7%), Unknown: 4 (1.6%)</t>
         </is>
       </c>
       <c r="Q18" s="4" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>3: 116 (78.9%), 2c: 29 (19.7%), 2a: 1 (0.7%), 2b: 1 (0.7%)</t>
+          <t>3: 116 (46.8%), 2c: 29 (11.7%), 2a: 1 (0.4%), 2b: 1 (0.4%), Unknown: 101 (40.7%)</t>
         </is>
       </c>
       <c r="Q29" s="4" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>M: 75 (50.3%), F: 74 (49.7%)</t>
+          <t>M: 75 (50.0%), F: 74 (49.3%), Unknown: 1 (0.7%)</t>
         </is>
       </c>
       <c r="Q4" s="4" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>M: 57 (60.6%), F: 37 (39.4%)</t>
+          <t>M: 57 (58.2%), F: 37 (37.8%), Unknown: 4 (4.1%)</t>
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>0: 108 (73.0%), 1: 40 (27.0%)</t>
+          <t>0: 108 (72.0%), 1: 40 (26.7%), Unknown: 2 (1.3%)</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>0: 66 (69.5%), 1: 29 (30.5%)</t>
+          <t>0: 66 (67.3%), 1: 29 (29.6%), Unknown: 3 (3.1%)</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>1: 86 (57.7%), 0: 63 (42.3%)</t>
+          <t>1: 86 (57.3%), 0: 63 (42.0%), Unknown: 1 (0.7%)</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>1: 65 (68.4%), 0: 30 (31.6%)</t>
+          <t>1: 65 (66.3%), 0: 30 (30.6%), Unknown: 3 (3.1%)</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>0: 124 (83.8%), 1: 24 (16.2%)</t>
+          <t>0: 124 (82.7%), 1: 24 (16.0%), Unknown: 2 (1.3%)</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>0: 79 (84.0%), 1: 15 (16.0%)</t>
+          <t>0: 79 (80.6%), 1: 15 (15.3%), Unknown: 4 (4.1%)</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>0: 100 (68.5%), 1: 46 (31.5%)</t>
+          <t>0: 100 (66.7%), 1: 46 (30.7%), Unknown: 4 (2.7%)</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>0: 51 (53.7%), 1: 44 (46.3%)</t>
+          <t>0: 51 (52.0%), 1: 44 (44.9%), Unknown: 3 (3.1%)</t>
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>0: 120 (81.6%), 1: 27 (18.4%)</t>
+          <t>0: 120 (80.0%), 1: 27 (18.0%), Unknown: 3 (2.0%)</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>0: 78 (84.8%), 1: 14 (15.2%)</t>
+          <t>0: 78 (79.6%), 1: 14 (14.3%), Unknown: 6 (6.1%)</t>
         </is>
       </c>
       <c r="Q17" s="4" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>0: 102 (70.3%), 1: 43 (29.7%)</t>
+          <t>0: 102 (68.0%), 1: 43 (28.7%), Unknown: 5 (3.3%)</t>
         </is>
       </c>
       <c r="Q18" s="4" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>0: 55 (58.5%), 1: 39 (41.5%)</t>
+          <t>0: 55 (56.1%), 1: 39 (39.8%), Unknown: 4 (4.1%)</t>
         </is>
       </c>
       <c r="Q19" s="4" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>0: 110 (75.3%), 1: 36 (24.7%)</t>
+          <t>0: 110 (73.3%), 1: 36 (24.0%), Unknown: 4 (2.7%)</t>
         </is>
       </c>
       <c r="Q20" s="4" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>0: 70 (74.5%), 1: 24 (25.5%)</t>
+          <t>0: 70 (71.4%), 1: 24 (24.5%), Unknown: 4 (4.1%)</t>
         </is>
       </c>
       <c r="Q21" s="4" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>0: 106 (71.6%), 1: 42 (28.4%)</t>
+          <t>0: 106 (70.7%), 1: 42 (28.0%), Unknown: 2 (1.3%)</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>0: 71 (75.5%), 1: 23 (24.5%)</t>
+          <t>0: 71 (72.4%), 1: 23 (23.5%), Unknown: 4 (4.1%)</t>
         </is>
       </c>
       <c r="Q31" s="4" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>0: 130 (94.9%), 1: 7 (5.1%)</t>
+          <t>0: 130 (86.7%), 1: 7 (4.7%), Unknown: 13 (8.7%)</t>
         </is>
       </c>
       <c r="Q32" s="4" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>0: 82 (98.8%), 1: 1 (1.2%)</t>
+          <t>0: 82 (83.7%), 1: 1 (1.0%), Unknown: 15 (15.3%)</t>
         </is>
       </c>
       <c r="Q33" s="4" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>0: 130 (87.2%), 1: 19 (12.8%)</t>
+          <t>0: 130 (86.7%), 1: 19 (12.7%), Unknown: 1 (0.7%)</t>
         </is>
       </c>
       <c r="Q34" s="4" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>0: 85 (89.5%), 1: 10 (10.5%)</t>
+          <t>0: 85 (86.7%), 1: 10 (10.2%), Unknown: 3 (3.1%)</t>
         </is>
       </c>
       <c r="Q35" s="4" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>3: 75 (75.8%), 2c: 22 (22.2%), 2a: 1 (1.0%), 2b: 1 (1.0%)</t>
+          <t>3: 75 (50.0%), 2c: 22 (14.7%), 2a: 1 (0.7%), 2b: 1 (0.7%), Unknown: 51 (34.0%)</t>
         </is>
       </c>
       <c r="Q56" s="4" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>3: 41 (85.4%), 2c: 7 (14.6%)</t>
+          <t>3: 41 (41.8%), 2c: 7 (7.1%), Unknown: 50 (51.0%)</t>
         </is>
       </c>
       <c r="Q57" s="4" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>M: 53 (55.8%), F: 42 (44.2%)</t>
+          <t>M: 53 (53.0%), F: 42 (42.0%), Unknown: 5 (5.0%)</t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>0: 98 (67.1%), 1: 48 (32.9%)</t>
+          <t>0: 98 (66.2%), 1: 48 (32.4%), Unknown: 2 (1.4%)</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>0: 76 (78.4%), 1: 21 (21.6%)</t>
+          <t>0: 76 (76.0%), 1: 21 (21.0%), Unknown: 3 (3.0%)</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>1: 88 (59.9%), 0: 59 (40.1%)</t>
+          <t>1: 88 (59.5%), 0: 59 (39.9%), Unknown: 1 (0.7%)</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
@@ -11394,7 +11394,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>1: 63 (64.9%), 0: 34 (35.1%)</t>
+          <t>1: 63 (63.0%), 0: 34 (34.0%), Unknown: 3 (3.0%)</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
@@ -11484,7 +11484,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>0: 122 (83.6%), 1: 24 (16.4%)</t>
+          <t>0: 122 (82.4%), 1: 24 (16.2%), Unknown: 2 (1.4%)</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>0: 81 (84.4%), 1: 15 (15.6%)</t>
+          <t>0: 81 (81.0%), 1: 15 (15.0%), Unknown: 4 (4.0%)</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>0: 105 (72.9%), 1: 39 (27.1%)</t>
+          <t>0: 105 (70.9%), 1: 39 (26.4%), Unknown: 4 (2.7%)</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
@@ -11754,7 +11754,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>1: 51 (52.6%), 0: 46 (47.4%)</t>
+          <t>1: 51 (51.0%), 0: 46 (46.0%), Unknown: 3 (3.0%)</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>0: 112 (77.8%), 1: 32 (22.2%)</t>
+          <t>0: 112 (75.7%), 1: 32 (21.6%), Unknown: 4 (2.7%)</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>0: 86 (90.5%), 1: 9 (9.5%)</t>
+          <t>0: 86 (86.0%), 1: 9 (9.0%), Unknown: 5 (5.0%)</t>
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>0: 93 (65.5%), 1: 49 (34.5%)</t>
+          <t>0: 93 (62.8%), 1: 49 (33.1%), Unknown: 6 (4.1%)</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>0: 64 (66.0%), 1: 33 (34.0%)</t>
+          <t>0: 64 (64.0%), 1: 33 (33.0%), Unknown: 3 (3.0%)</t>
         </is>
       </c>
       <c r="Q17" s="4" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>0: 101 (70.6%), 1: 42 (29.4%)</t>
+          <t>0: 101 (68.2%), 1: 42 (28.4%), Unknown: 5 (3.4%)</t>
         </is>
       </c>
       <c r="Q18" s="4" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>0: 79 (81.4%), 1: 18 (18.6%)</t>
+          <t>0: 79 (79.0%), 1: 18 (18.0%), Unknown: 3 (3.0%)</t>
         </is>
       </c>
       <c r="Q19" s="4" t="inlineStr">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>0: 88 (60.3%), 1: 58 (39.7%)</t>
+          <t>0: 88 (59.5%), 1: 58 (39.2%), Unknown: 2 (1.4%)</t>
         </is>
       </c>
       <c r="Q28" s="4" t="inlineStr">
@@ -13094,7 +13094,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>0: 89 (92.7%), 1: 7 (7.3%)</t>
+          <t>0: 89 (89.0%), 1: 7 (7.0%), Unknown: 4 (4.0%)</t>
         </is>
       </c>
       <c r="Q29" s="4" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>0: 116 (94.3%), 1: 7 (5.7%)</t>
+          <t>0: 116 (78.4%), 1: 7 (4.7%), Unknown: 25 (16.9%)</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>0: 96 (99.0%), 1: 1 (1.0%)</t>
+          <t>0: 96 (96.0%), 1: 1 (1.0%), Unknown: 3 (3.0%)</t>
         </is>
       </c>
       <c r="Q31" s="4" t="inlineStr">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>0: 127 (86.4%), 1: 20 (13.6%)</t>
+          <t>0: 127 (85.8%), 1: 20 (13.5%), Unknown: 1 (0.7%)</t>
         </is>
       </c>
       <c r="Q32" s="4" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>0: 88 (90.7%), 1: 9 (9.3%)</t>
+          <t>0: 88 (88.0%), 1: 9 (9.0%), Unknown: 3 (3.0%)</t>
         </is>
       </c>
       <c r="Q33" s="4" t="inlineStr">
@@ -15084,7 +15084,7 @@
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>3: 116 (78.9%), 2c: 29 (19.7%), 2a: 1 (0.7%), 2b: 1 (0.7%)</t>
+          <t>3: 116 (78.4%), 2c: 29 (19.6%), 2a: 1 (0.7%), 2b: 1 (0.7%), Unknown: 1 (0.7%)</t>
         </is>
       </c>
       <c r="Q54" s="4" t="inlineStr">
@@ -15172,9 +15172,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P55" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>Unknown: 100 (100.0%)</t>
         </is>
       </c>
       <c r="Q55" s="4" t="inlineStr">
